--- a/artfynd/A 35213-2019 artfynd.xlsx
+++ b/artfynd/A 35213-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35213-2019 artfynd.xlsx
+++ b/artfynd/A 35213-2019 artfynd.xlsx
@@ -1551,7 +1551,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124390796</v>
+        <v>124390590</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595539</v>
+        <v>595492</v>
       </c>
       <c r="R9" t="n">
-        <v>6651097</v>
+        <v>6651044</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1645,6 +1645,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>8 stänglar</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1657,7 +1662,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Granskog på ås.. Knäroten finns på ett litet utrymme mellan mossbelupna stenblock i slutning.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1675,7 +1685,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124390590</v>
+        <v>124390796</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1710,7 +1720,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1731,10 +1741,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595492</v>
+        <v>595539</v>
       </c>
       <c r="R10" t="n">
-        <v>6651044</v>
+        <v>6651097</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1769,11 +1779,6 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>8 stänglar</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1786,12 +1791,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Granskog på ås.. Knäroten finns på ett litet utrymme mellan mossbelupna stenblock i slutning.</t>
+          <t>Ängsgranskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 35213-2019 artfynd.xlsx
+++ b/artfynd/A 35213-2019 artfynd.xlsx
@@ -1307,7 +1307,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124358904</v>
+        <v>124359517</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1353,17 +1353,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Härsta 6 (knärot), Upl</t>
+          <t>Härsta 1 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595492</v>
+        <v>595757</v>
       </c>
       <c r="R7" t="n">
-        <v>6651057</v>
+        <v>6651149</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>U-Sal-0476</t>
+          <t>U-Sal-0462</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1429,7 +1429,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124359517</v>
+        <v>124358904</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1475,17 +1475,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Härsta 1 (knärot), Upl</t>
+          <t>Härsta 6 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595757</v>
+        <v>595492</v>
       </c>
       <c r="R8" t="n">
-        <v>6651149</v>
+        <v>6651057</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-0462</t>
+          <t>U-Sal-0476</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1551,7 +1551,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124390590</v>
+        <v>124390796</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595492</v>
+        <v>595539</v>
       </c>
       <c r="R9" t="n">
-        <v>6651044</v>
+        <v>6651097</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1645,11 +1645,6 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>8 stänglar</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1662,12 +1657,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Granskog på ås.. Knäroten finns på ett litet utrymme mellan mossbelupna stenblock i slutning.</t>
+          <t>Ängsgranskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1685,7 +1675,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124390796</v>
+        <v>124390590</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1720,7 +1710,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1741,10 +1731,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595539</v>
+        <v>595492</v>
       </c>
       <c r="R10" t="n">
-        <v>6651097</v>
+        <v>6651044</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,6 +1769,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>8 stänglar</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1791,7 +1786,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Granskog på ås.. Knäroten finns på ett litet utrymme mellan mossbelupna stenblock i slutning.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 35213-2019 artfynd.xlsx
+++ b/artfynd/A 35213-2019 artfynd.xlsx
@@ -1307,7 +1307,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124359517</v>
+        <v>124358904</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1353,17 +1353,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Härsta 1 (knärot), Upl</t>
+          <t>Härsta 6 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595757</v>
+        <v>595492</v>
       </c>
       <c r="R7" t="n">
-        <v>6651149</v>
+        <v>6651057</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>U-Sal-0462</t>
+          <t>U-Sal-0476</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1429,7 +1429,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124358904</v>
+        <v>124359517</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1475,17 +1475,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Härsta 6 (knärot), Upl</t>
+          <t>Härsta 1 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595492</v>
+        <v>595757</v>
       </c>
       <c r="R8" t="n">
-        <v>6651057</v>
+        <v>6651149</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-0476</t>
+          <t>U-Sal-0462</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">

--- a/artfynd/A 35213-2019 artfynd.xlsx
+++ b/artfynd/A 35213-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124360176</v>
+        <v>124359495</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -721,17 +721,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härsta 7 (knärot), Upl</t>
+          <t>Härsta 8 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595901</v>
+        <v>595879</v>
       </c>
       <c r="R2" t="n">
-        <v>6651357</v>
+        <v>6651329</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>U-Sal-0606</t>
+          <t>U-Sal-0614</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124359495</v>
+        <v>124360176</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -843,17 +843,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härsta 8 (knärot), Upl</t>
+          <t>Härsta 7 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595879</v>
+        <v>595901</v>
       </c>
       <c r="R3" t="n">
-        <v>6651329</v>
+        <v>6651357</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>U-Sal-0614</t>
+          <t>U-Sal-0606</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1551,7 +1551,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124390796</v>
+        <v>124390590</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595539</v>
+        <v>595492</v>
       </c>
       <c r="R9" t="n">
-        <v>6651097</v>
+        <v>6651044</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1645,6 +1645,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>8 stänglar</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1657,7 +1662,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Granskog på ås.. Knäroten finns på ett litet utrymme mellan mossbelupna stenblock i slutning.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1675,7 +1685,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124390590</v>
+        <v>124390796</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1710,7 +1720,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1731,10 +1741,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595492</v>
+        <v>595539</v>
       </c>
       <c r="R10" t="n">
-        <v>6651044</v>
+        <v>6651097</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1769,11 +1779,6 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>8 stänglar</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1786,12 +1791,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Granskog på ås.. Knäroten finns på ett litet utrymme mellan mossbelupna stenblock i slutning.</t>
+          <t>Ängsgranskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 35213-2019 artfynd.xlsx
+++ b/artfynd/A 35213-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124359495</v>
+        <v>124360176</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -721,17 +721,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härsta 8 (knärot), Upl</t>
+          <t>Härsta 7 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595879</v>
+        <v>595901</v>
       </c>
       <c r="R2" t="n">
-        <v>6651329</v>
+        <v>6651357</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>U-Sal-0614</t>
+          <t>U-Sal-0606</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124360176</v>
+        <v>124359495</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -843,17 +843,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härsta 7 (knärot), Upl</t>
+          <t>Härsta 8 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595901</v>
+        <v>595879</v>
       </c>
       <c r="R3" t="n">
-        <v>6651357</v>
+        <v>6651329</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>U-Sal-0606</t>
+          <t>U-Sal-0614</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">

--- a/artfynd/A 35213-2019 artfynd.xlsx
+++ b/artfynd/A 35213-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124360176</v>
+        <v>124359495</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -721,17 +721,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härsta 7 (knärot), Upl</t>
+          <t>Härsta 8 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595901</v>
+        <v>595879</v>
       </c>
       <c r="R2" t="n">
-        <v>6651357</v>
+        <v>6651329</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>U-Sal-0606</t>
+          <t>U-Sal-0614</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124359495</v>
+        <v>124360176</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -843,17 +843,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härsta 8 (knärot), Upl</t>
+          <t>Härsta 7 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595879</v>
+        <v>595901</v>
       </c>
       <c r="R3" t="n">
-        <v>6651329</v>
+        <v>6651357</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>U-Sal-0614</t>
+          <t>U-Sal-0606</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">

--- a/artfynd/A 35213-2019 artfynd.xlsx
+++ b/artfynd/A 35213-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124359495</v>
+        <v>124360176</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -721,17 +721,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härsta 8 (knärot), Upl</t>
+          <t>Härsta 7 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595879</v>
+        <v>595901</v>
       </c>
       <c r="R2" t="n">
-        <v>6651329</v>
+        <v>6651357</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>U-Sal-0614</t>
+          <t>U-Sal-0606</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124360176</v>
+        <v>124359495</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -843,17 +843,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härsta 7 (knärot), Upl</t>
+          <t>Härsta 8 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595901</v>
+        <v>595879</v>
       </c>
       <c r="R3" t="n">
-        <v>6651357</v>
+        <v>6651329</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>U-Sal-0606</t>
+          <t>U-Sal-0614</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124359517</v>
+        <v>124358904</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1353,17 +1353,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Härsta 1 (knärot), Upl</t>
+          <t>Härsta 6 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595757</v>
+        <v>595492</v>
       </c>
       <c r="R7" t="n">
-        <v>6651149</v>
+        <v>6651057</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>U-Sal-0462</t>
+          <t>U-Sal-0476</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1429,7 +1429,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124358904</v>
+        <v>124359517</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1475,17 +1475,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Härsta 6 (knärot), Upl</t>
+          <t>Härsta 1 (knärot), Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595492</v>
+        <v>595757</v>
       </c>
       <c r="R8" t="n">
-        <v>6651057</v>
+        <v>6651149</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>U-Sal-0476</t>
+          <t>U-Sal-0462</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
